--- a/data/测试数据.xlsx
+++ b/data/测试数据.xlsx
@@ -3,13 +3,13 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-360" yWindow="3108" windowWidth="17028" windowHeight="12120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="3000" windowWidth="26004" windowHeight="12120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -64,7 +64,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -87,11 +87,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -106,6 +119,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -450,13 +466,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="11.4"/>
   <cols>
-    <col width="8.88671875" customWidth="1" style="1" min="1" max="3"/>
+    <col width="8.88671875" customWidth="1" style="1" min="1" max="2"/>
+    <col width="11.5546875" customWidth="1" style="1" min="3" max="3"/>
     <col width="24.77734375" customWidth="1" style="1" min="4" max="4"/>
     <col width="8.88671875" customWidth="1" style="1" min="5" max="5"/>
-    <col width="21.44140625" customWidth="1" style="1" min="6" max="6"/>
+    <col width="23.6640625" customWidth="1" style="1" min="6" max="6"/>
     <col width="21.33203125" customWidth="1" style="1" min="7" max="7"/>
     <col width="23.33203125" customWidth="1" style="1" min="8" max="8"/>
     <col width="33.44140625" customWidth="1" style="1" min="9" max="9"/>
@@ -468,7 +485,8 @@
     <col width="26.109375" customWidth="1" style="1" min="15" max="15"/>
     <col width="16" customWidth="1" style="1" min="16" max="16"/>
     <col width="32.109375" customWidth="1" style="1" min="17" max="17"/>
-    <col width="8.88671875" customWidth="1" style="1" min="18" max="16384"/>
+    <col width="8.88671875" customWidth="1" style="1" min="18" max="19"/>
+    <col width="8.88671875" customWidth="1" style="1" min="20" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -944,6 +962,7 @@
       <c r="H7" s="4" t="n"/>
       <c r="I7" s="4" t="n"/>
       <c r="J7" s="4" t="n"/>
+      <c r="K7" s="3" t="n"/>
       <c r="L7" s="4" t="inlineStr">
         <is>
           <t>$..msg</t>
@@ -962,33 +981,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" ht="22.8" customHeight="1">
-      <c r="A8" s="3" t="n">
+    <row r="8">
+      <c r="A8" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>图片上传</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>上传成功</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>图片上传成功</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>/upload</t>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>用户管理</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>删除成功</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>删除用户，删除成功</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>/users/{{JAY_ID}}</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -996,31 +1015,328 @@
           <t>{"Authorization":"{{token}}"}</t>
         </is>
       </c>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="n"/>
-      <c r="K8" s="6" t="inlineStr">
-        <is>
-          <t>{"file":("1.png",open("./file/1.png","rb"),"image/png")}</t>
-        </is>
-      </c>
+      <c r="H8" s="4" t="n"/>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="4" t="n"/>
+      <c r="K8" s="3" t="n"/>
       <c r="L8" s="4" t="inlineStr">
         <is>
           <t>$..msg</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>上传成功</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="n"/>
-      <c r="O8" s="3" t="n"/>
-      <c r="P8" s="3" t="n"/>
-      <c r="Q8" s="3" t="n"/>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>删除成功</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="n"/>
+      <c r="O8" s="4" t="n"/>
+      <c r="P8" s="4" t="n"/>
+      <c r="Q8" s="4" t="n"/>
       <c r="R8" s="4" t="b">
         <v>1</v>
       </c>
+    </row>
+    <row r="9" ht="22.8" customHeight="1">
+      <c r="A9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>图片上传</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>上传成功</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>图片上传成功</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>/upload</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>{"Authorization":"{{token}}"}</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="n"/>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>{"file":("1.png",open("./file/1.png","rb"),"image/png")}</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>$..msg</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>上传成功</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="n"/>
+      <c r="O9" s="3" t="n"/>
+      <c r="P9" s="3" t="n"/>
+      <c r="Q9" s="3" t="n"/>
+      <c r="R9" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>商品管理</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>查询成功</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>查询商品列表查询成功</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>get</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>/goods</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>{"Authorization":"{{token}}"}</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> {"pagenum": 1, "pagesize": 1}</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="n"/>
+      <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="n"/>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>$..msg</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>获取成功</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="n"/>
+      <c r="O10" s="3" t="n"/>
+      <c r="P10" s="4" t="n"/>
+      <c r="Q10" s="3" t="n"/>
+      <c r="R10" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>商品管理</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>创建成功</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>添加商品，添加成功</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>/goods</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>{"Authorization":"{{token}}"}</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>{"goods_name": "测试商品{{now}}", "goods_price": 100, "goods_number": 10, "goods_weight": 1, "goods_cat": "1,3,5"}</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>$..msg</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>创建商品成功</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="n"/>
+      <c r="O11" s="3" t="n"/>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>{"SHOP_ID":"$..goods_id"}</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="n"/>
+      <c r="R11" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>商品管理</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>修改成功</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>修改商品，修改成功</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>put</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>/goods/{{SHOP_ID}}/state/1</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>{"Authorization":"{{token}}"}</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="3" t="n"/>
+      <c r="J12" s="3" t="n"/>
+      <c r="K12" s="3" t="n"/>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>$..msg</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>更新成功</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="n"/>
+      <c r="O12" s="3" t="n"/>
+      <c r="P12" s="3" t="n"/>
+      <c r="Q12" s="3" t="n"/>
+      <c r="R12" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>商品管理</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>删除成功</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>删除商品，删除成功</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>/goods/{{SHOP_ID}}</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>{"Authorization":"{{token}}"}</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="n"/>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>$..msg</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>删除成功</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="n"/>
+      <c r="O13" s="3" t="n"/>
+      <c r="P13" s="3" t="n"/>
+      <c r="Q13" s="3" t="n"/>
+      <c r="R13" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="G14" s="7" t="n"/>
+      <c r="L14" s="7" t="n"/>
+      <c r="M14" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
